--- a/data/Equipment/affix.xlsx
+++ b/data/Equipment/affix.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>attack:1</t>
+          <t>Attack:1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>attack:2</t>
+          <t>Attack:2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>attack:3</t>
+          <t>Attack:3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>attack:4</t>
+          <t>Attack:4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>attack:5</t>
+          <t>Attack:5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>armor:1</t>
+          <t>Armor:1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>armor:2</t>
+          <t>Armor:2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>armor:3</t>
+          <t>Armor:3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>armor:4</t>
+          <t>Armor:4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>armor:5</t>
+          <t>Armor:5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>attack:1|armor:1</t>
+          <t>Attack:1|Armor:1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>attack:2|armor:2</t>
+          <t>Attack:2|Armor:2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>attack:3|armor:3</t>
+          <t>Attack:3|Armor:3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>attack:4|armor:4</t>
+          <t>Attack:4|Armor:4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>attack:5|armor:5</t>
+          <t>Attack:5|Armor:5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>crit_rate:1</t>
+          <t>CritRate:1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>crit_rate:2</t>
+          <t>CritRate:2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>crit_rate:3</t>
+          <t>CritRate:3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>crit_rate:4</t>
+          <t>CritRate:4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>crit_rate:5</t>
+          <t>CritRate:5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">

--- a/data/Equipment/affix.xlsx
+++ b/data/Equipment/affix.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>(dict#sep=|),StatType,float</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
